--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1197,51 +1197,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1313,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1352,7 +1348,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -1386,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1463,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1504,9 +1500,9 @@
       <c r="I14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1536,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1643,7 +1639,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1651,47 +1647,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1836,12 +1836,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1946,9 +1946,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -1979,19 +1979,19 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2111,15 +2111,15 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2129,19 +2129,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2246,17 +2246,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2279,19 +2279,19 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2393,33 +2393,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2554,22 +2554,22 @@
       <c r="I28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2693,59 +2693,55 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2817,12 +2813,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2847,7 +2843,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2856,24 +2852,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2890,12 +2886,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2967,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3000,17 +2996,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3040,12 +3036,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3070,7 +3066,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3078,8 +3074,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3088,37 +3086,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3151,8 +3151,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>4</v>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3161,37 +3163,39 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3216,7 +3220,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3224,47 +3228,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3332,12 +3340,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3362,7 +3370,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3370,8 +3378,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>1</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3380,37 +3390,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3438,17 +3450,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3478,12 +3490,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3508,7 +3520,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3516,10 +3528,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3528,39 +3538,37 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3585,33 +3593,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3628,12 +3636,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3658,7 +3666,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3666,51 +3674,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3735,7 +3739,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3744,24 +3748,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3778,12 +3782,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3808,7 +3812,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3816,10 +3820,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3828,39 +3830,37 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3894,11 +3894,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4005,12 +4005,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4038,17 +4038,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4078,12 +4078,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4185,33 +4185,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4335,33 +4335,33 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4485,33 +4485,33 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>45</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4635,33 +4635,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4716,8 +4716,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4726,37 +4728,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4781,33 +4785,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4824,12 +4828,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4854,7 +4858,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4862,47 +4866,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4927,33 +4935,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4970,12 +4978,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5000,7 +5008,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5008,8 +5016,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>1</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5018,37 +5028,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5073,7 +5085,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5082,24 +5094,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5116,12 +5128,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5146,7 +5158,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5154,10 +5166,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5166,39 +5176,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5232,11 +5240,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5266,12 +5274,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5307,9 +5315,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5327,7 +5335,7 @@
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
@@ -5339,12 +5347,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5382,7 +5390,7 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5412,12 +5420,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5451,11 +5459,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5485,12 +5493,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5518,17 +5526,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5558,12 +5566,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5588,7 +5596,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5596,8 +5604,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5606,37 +5616,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5661,7 +5673,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5670,24 +5682,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5704,12 +5716,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5765,7 +5777,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -5777,12 +5789,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5816,11 +5828,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5850,12 +5862,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5923,12 +5935,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5956,17 +5968,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -5996,12 +6008,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6069,12 +6081,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6099,7 +6111,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6108,24 +6120,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6142,82 +6154,520 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -750,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1647,10 +1647,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1659,39 +1657,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1763,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1793,7 +1789,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1801,8 +1797,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1811,37 +1809,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1954,9 +1954,9 @@
       <c r="I20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1986,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,14 +2063,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2102,11 +2102,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,14 +2213,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2252,11 +2252,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2363,14 +2363,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2396,17 +2396,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,14 +2513,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2543,33 +2543,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2663,14 +2663,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2693,33 +2693,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,14 +2813,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2843,33 +2843,33 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2886,12 +2886,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2963,14 +2963,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3006,20 +3006,20 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3113,14 +3113,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3151,10 +3151,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I36" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3163,39 +3161,37 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3267,14 +3263,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3297,7 +3293,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3305,8 +3301,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3315,37 +3313,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3417,14 +3417,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3450,17 +3450,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3490,14 +3490,14 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3528,8 +3528,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -3538,39 +3540,41 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3593,33 +3597,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3636,12 +3640,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3677,9 +3681,9 @@
       <c r="I43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -3697,7 +3701,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -3709,14 +3713,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3739,7 +3743,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3748,7 +3752,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3757,15 +3761,15 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3782,14 +3786,14 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3821,11 +3825,11 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -3843,7 +3847,7 @@
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -3855,12 +3859,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3928,14 +3932,14 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3958,7 +3962,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3966,10 +3970,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3978,41 +3980,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4038,17 +4038,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4078,12 +4078,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4155,14 +4155,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4185,33 +4185,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4305,14 +4305,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4344,24 +4344,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 73,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4378,12 +4378,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4455,14 +4455,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4494,11 +4494,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4605,14 +4605,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4638,17 +4638,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4755,14 +4755,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4785,33 +4785,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4828,12 +4828,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4946,9 +4946,9 @@
       <c r="I60" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5055,14 +5055,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5090,20 +5090,20 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5128,14 +5128,14 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5166,8 +5166,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5176,39 +5178,41 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5231,7 +5235,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5240,24 +5244,24 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5274,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5315,9 +5319,9 @@
       <c r="I65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -5347,14 +5351,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5386,11 +5390,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5420,14 +5424,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5459,11 +5463,11 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5493,14 +5497,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5532,11 +5536,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5566,14 +5570,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5596,7 +5600,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5604,10 +5608,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5616,41 +5618,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5682,11 +5682,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5716,14 +5716,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5754,8 +5754,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5764,39 +5766,41 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5828,11 +5832,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5862,12 +5866,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5903,9 +5907,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5923,7 +5927,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5935,14 +5939,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5968,17 +5972,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6008,14 +6012,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6047,11 +6051,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6081,14 +6085,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6111,33 +6115,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6154,14 +6158,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6193,7 +6197,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6227,14 +6231,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6257,7 +6261,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6266,24 +6270,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6300,12 +6304,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6341,9 +6345,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6373,14 +6377,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6412,11 +6416,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6446,14 +6450,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6485,11 +6489,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6519,14 +6523,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6558,11 +6562,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6592,82 +6596,228 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,51 +1797,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1952,7 +1948,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1986,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2104,9 +2100,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2136,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2243,7 +2239,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2251,47 +2247,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2436,12 +2436,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2546,9 +2546,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -2579,19 +2579,19 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2663,12 +2663,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2711,15 +2711,15 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2729,19 +2729,19 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2879,19 +2879,19 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2993,33 +2993,33 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L34" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3113,12 +3113,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3154,22 +3154,22 @@
       <c r="I36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3293,59 +3293,55 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3417,12 +3413,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3447,7 +3443,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3456,24 +3452,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3490,12 +3486,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3567,12 +3563,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3600,17 +3596,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3640,12 +3636,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3670,7 +3666,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3678,8 +3674,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>0</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3688,37 +3686,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3751,8 +3751,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n">
-        <v>4</v>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3761,37 +3763,39 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3816,7 +3820,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3824,47 +3828,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3932,12 +3940,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3962,7 +3970,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3970,8 +3978,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>1</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3980,37 +3990,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4038,17 +4050,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4078,12 +4090,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4108,7 +4120,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4116,10 +4128,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4128,39 +4138,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4185,33 +4193,33 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4228,12 +4236,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4258,7 +4266,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4266,51 +4274,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4335,7 +4339,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4344,24 +4348,24 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4378,12 +4382,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4408,7 +4412,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4416,10 +4420,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4428,39 +4430,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4494,11 +4494,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4638,17 +4638,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4785,33 +4785,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4828,12 +4828,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4935,33 +4935,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5085,33 +5085,33 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>45</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5235,33 +5235,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5278,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5316,8 +5316,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5326,37 +5328,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5381,33 +5385,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5424,12 +5428,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5454,7 +5458,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5462,47 +5466,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5527,33 +5535,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5570,12 +5578,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5600,7 +5608,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5608,8 +5616,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>1</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5618,37 +5628,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5673,7 +5685,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5682,24 +5694,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5716,12 +5728,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5746,7 +5758,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5754,10 +5766,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5766,39 +5776,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5832,11 +5840,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5866,12 +5874,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5907,9 +5915,9 @@
       <c r="I73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5927,7 +5935,7 @@
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
@@ -5939,12 +5947,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5982,7 +5990,7 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6012,12 +6020,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6051,11 +6059,11 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -6085,12 +6093,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6118,17 +6126,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6158,12 +6166,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6188,7 +6196,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6196,8 +6204,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>1</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6206,37 +6216,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6261,7 +6273,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6270,24 +6282,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6304,12 +6316,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6365,7 +6377,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6377,12 +6389,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6416,11 +6428,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6450,12 +6462,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6523,12 +6535,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6556,17 +6568,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6596,12 +6608,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6669,12 +6681,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6699,7 +6711,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6708,24 +6720,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6742,82 +6754,520 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2098,11 +2098,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2247,51 +2247,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2363,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2402,7 +2398,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2436,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2554,9 +2550,9 @@
       <c r="I28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2586,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2663,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2693,7 +2689,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2701,47 +2697,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2886,12 +2886,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2996,9 +2996,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
@@ -3029,19 +3029,19 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3113,12 +3113,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3161,15 +3161,15 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3179,19 +3179,19 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3329,19 +3329,19 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3443,33 +3443,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3604,22 +3604,22 @@
       <c r="I42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3713,12 +3713,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3743,59 +3743,55 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3867,12 +3863,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3897,7 +3893,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3906,24 +3902,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3940,12 +3936,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4017,12 +4013,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4050,17 +4046,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4090,12 +4086,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4120,7 +4116,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4128,8 +4124,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4138,37 +4136,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4201,8 +4201,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>4</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4211,37 +4213,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4266,7 +4270,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4274,47 +4278,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4382,12 +4390,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4412,7 +4420,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4420,8 +4428,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>1</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4430,37 +4440,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4488,17 +4500,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4528,12 +4540,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4558,7 +4570,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4566,10 +4578,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4578,39 +4588,37 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4635,33 +4643,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4678,12 +4686,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4708,7 +4716,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4716,51 +4724,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4785,7 +4789,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4794,24 +4798,24 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4828,12 +4832,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4858,7 +4862,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4866,10 +4870,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4878,39 +4880,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4944,11 +4944,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4978,12 +4978,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5088,17 +5088,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5235,33 +5235,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5278,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5385,33 +5385,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5535,33 +5535,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>45</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5685,33 +5685,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>12</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5728,12 +5728,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5766,8 +5766,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5776,37 +5778,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5831,33 +5835,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5874,12 +5878,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5904,7 +5908,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5912,47 +5916,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5977,33 +5985,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6020,12 +6028,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6050,7 +6058,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6058,8 +6066,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6068,37 +6078,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6123,7 +6135,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6132,24 +6144,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6166,12 +6178,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6196,7 +6208,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6204,10 +6216,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6216,39 +6226,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6282,11 +6290,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6316,12 +6324,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6357,9 +6365,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J79" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6377,7 +6385,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
@@ -6389,12 +6397,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6432,7 +6440,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6462,12 +6470,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6501,11 +6509,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6535,12 +6543,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6568,17 +6576,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6608,12 +6616,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6638,7 +6646,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6646,8 +6654,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>1</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6656,37 +6666,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6711,7 +6723,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6720,24 +6732,24 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L84" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -6754,12 +6766,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6815,7 +6827,7 @@
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
@@ -6827,12 +6839,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6866,11 +6878,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6900,12 +6912,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6973,12 +6985,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7006,17 +7018,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7046,12 +7058,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7119,12 +7131,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7149,7 +7161,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7158,24 +7170,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>11</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7192,82 +7204,520 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -750,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1648,7 +1648,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,9 +1800,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,14 +2659,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2697,10 +2697,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2709,39 +2707,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2813,14 +2809,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2843,7 +2839,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2851,8 +2847,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2861,37 +2859,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3004,9 +3004,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3113,14 +3113,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3152,11 +3152,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3263,14 +3263,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3302,11 +3302,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3413,14 +3413,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3446,17 +3446,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3479,19 +3479,19 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3563,14 +3563,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3593,33 +3593,33 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3713,14 +3713,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3743,33 +3743,33 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3863,14 +3863,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3893,33 +3893,33 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4013,14 +4013,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4056,20 +4056,20 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4163,14 +4163,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4201,10 +4201,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4213,39 +4211,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4317,14 +4313,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4347,7 +4343,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4355,8 +4351,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4365,37 +4363,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4467,14 +4467,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4500,17 +4500,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4540,14 +4540,14 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4578,8 +4578,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4588,39 +4590,41 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4643,33 +4647,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4686,12 +4690,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4727,9 +4731,9 @@
       <c r="I57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4747,7 +4751,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
@@ -4759,14 +4763,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4789,7 +4793,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4798,7 +4802,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4807,15 +4811,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4832,14 +4836,14 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4871,11 +4875,11 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -4893,7 +4897,7 @@
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -4905,12 +4909,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4978,14 +4982,14 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5008,7 +5012,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5016,10 +5020,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5028,41 +5030,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5088,17 +5088,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5128,12 +5128,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5205,14 +5205,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5235,33 +5235,33 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -5278,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5355,14 +5355,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5394,24 +5394,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
-          <t>▼ 73,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5505,14 +5505,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5544,11 +5544,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5655,14 +5655,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5688,17 +5688,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5728,12 +5728,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5805,14 +5805,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5835,33 +5835,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5996,9 +5996,9 @@
       <c r="I74" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6105,14 +6105,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6140,20 +6140,20 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6178,14 +6178,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6216,8 +6216,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6226,39 +6228,41 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6281,7 +6285,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6290,24 +6294,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6324,12 +6328,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6365,9 +6369,9 @@
       <c r="I79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -6397,14 +6401,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6436,11 +6440,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6470,14 +6474,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6509,11 +6513,11 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -6543,14 +6547,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6582,11 +6586,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6616,14 +6620,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6646,7 +6650,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6654,10 +6658,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6666,41 +6668,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6732,11 +6732,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6766,14 +6766,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6804,8 +6804,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6814,39 +6816,41 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6878,11 +6882,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6912,12 +6916,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6953,9 +6957,9 @@
       <c r="I87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6973,7 +6977,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6985,14 +6989,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7018,17 +7022,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7058,14 +7062,14 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7097,11 +7101,11 @@
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -7131,14 +7135,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7161,33 +7165,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7204,14 +7208,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7243,7 +7247,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7277,14 +7281,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7307,7 +7311,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7316,24 +7320,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7350,12 +7354,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7391,9 +7395,9 @@
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7423,14 +7427,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7462,11 +7466,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7496,14 +7500,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7535,11 +7539,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7569,14 +7573,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7608,11 +7612,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7642,82 +7646,228 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,39 +680,37 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -742,17 +738,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +855,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +885,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,24 +894,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1005,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1044,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1194,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1348,11 +1344,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1455,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,11 +1494,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1682,12 +1678,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,9 +1796,9 @@
       <c r="I18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1828,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1948,11 +1944,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1978,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2055,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2098,11 +2094,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2128,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2248,11 +2244,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2278,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2432,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2505,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2552,7 +2548,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2582,12 +2578,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2655,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2698,11 +2694,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2732,12 +2728,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2805,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2839,7 +2835,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2847,10 +2843,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I32" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2859,39 +2853,37 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2963,12 +2955,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3036,12 +3028,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3113,12 +3105,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3143,7 +3135,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3151,47 +3143,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3263,12 +3259,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3302,11 +3298,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3336,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3413,12 +3409,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3452,11 +3448,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3486,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3563,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3596,17 +3592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3629,19 +3625,19 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3713,12 +3709,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3743,7 +3739,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3752,24 +3748,24 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -3779,19 +3775,19 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3863,12 +3859,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3902,11 +3898,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3936,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4013,12 +4009,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4054,9 +4050,9 @@
       <c r="I48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4069,7 +4065,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4086,12 +4082,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4163,12 +4159,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4196,17 +4192,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4236,12 +4232,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4313,12 +4309,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4343,7 +4339,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4351,51 +4347,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4467,12 +4459,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4506,7 +4498,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4540,12 +4532,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4617,12 +4609,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4647,55 +4639,59 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4720,7 +4716,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4728,8 +4724,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4738,37 +4736,39 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4811,15 +4811,15 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4836,12 +4836,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4874,47 +4874,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4942,17 +4946,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4982,12 +4986,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5021,7 +5025,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5055,12 +5059,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5085,7 +5089,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5094,7 +5098,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5103,15 +5107,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5128,12 +5132,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5158,7 +5162,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5166,51 +5170,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5238,17 +5238,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5278,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5316,10 +5316,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5328,39 +5326,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5385,7 +5381,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5394,24 +5390,24 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5428,12 +5424,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5505,12 +5501,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5538,17 +5534,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>▼ 73,3%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5578,12 +5574,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5655,12 +5651,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5685,7 +5681,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5694,24 +5690,24 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5728,12 +5724,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5805,12 +5801,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5838,17 +5834,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5878,12 +5874,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5955,12 +5951,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5985,33 +5981,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>45</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6028,12 +6024,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6105,12 +6101,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6135,33 +6131,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6178,12 +6174,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6255,12 +6251,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6290,20 +6286,20 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
@@ -6311,7 +6307,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6328,12 +6324,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6358,7 +6354,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6366,8 +6362,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6376,37 +6374,39 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6431,33 +6431,33 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>9</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6512,47 +6512,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6577,7 +6581,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6590,20 +6594,20 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6620,12 +6624,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6659,7 +6663,7 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6693,12 +6697,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6732,11 +6736,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>▲ 112,5%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6766,12 +6770,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6796,7 +6800,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6804,51 +6808,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6882,11 +6882,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6916,12 +6916,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6989,12 +6989,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7028,11 +7028,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>17</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7092,7 +7092,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7100,47 +7100,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7168,17 +7172,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>8</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7208,12 +7212,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7247,7 +7251,7 @@
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7269,7 +7273,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
@@ -7281,12 +7285,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7311,7 +7315,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7320,24 +7324,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7354,12 +7358,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7395,9 +7399,9 @@
       <c r="I93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -7427,12 +7431,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7460,17 +7464,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>13</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7500,12 +7504,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7539,11 +7543,11 @@
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7573,12 +7577,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7603,7 +7607,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7612,24 +7616,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>11</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7646,12 +7650,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7685,7 +7689,7 @@
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7719,12 +7723,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7758,11 +7762,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7792,82 +7796,374 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,8 +670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n">
-        <v>1</v>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -680,37 +682,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -738,17 +742,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -855,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -885,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -894,24 +898,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1005,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1046,9 +1050,9 @@
       <c r="I8" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1155,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1194,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1228,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1344,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1378,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1494,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1528,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1605,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1644,7 +1648,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1678,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1755,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,7 +1789,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1793,47 +1797,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1905,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1944,7 +1952,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1978,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2055,12 +2063,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2128,12 +2136,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2158,7 +2166,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2166,10 +2174,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2178,39 +2184,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2246,9 +2250,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2278,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2308,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2316,51 +2320,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2394,11 +2394,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2428,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2466,10 +2466,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2478,39 +2476,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2538,17 +2534,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2578,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2655,12 +2651,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2685,7 +2681,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2696,22 +2692,22 @@
       <c r="I30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2728,12 +2724,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2805,12 +2801,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2844,11 +2840,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2878,12 +2874,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2955,12 +2951,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2994,11 +2990,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3028,12 +3024,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3105,12 +3101,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3135,7 +3131,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3143,51 +3139,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3259,12 +3251,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3298,11 +3290,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3332,12 +3324,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3409,12 +3401,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3448,11 +3440,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3482,12 +3474,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,12 +3551,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3598,11 +3590,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3632,12 +3624,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3709,12 +3701,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3782,12 +3774,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3859,12 +3851,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3892,17 +3884,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3925,19 +3917,19 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4001,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4039,7 +4031,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4048,24 +4040,24 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -4075,19 +4067,19 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4159,12 +4151,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4192,17 +4184,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4225,19 +4217,19 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4309,12 +4301,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4339,7 +4331,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4357,15 +4349,15 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -4375,19 +4367,19 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4459,12 +4451,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4502,7 +4494,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4525,19 +4517,19 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4609,12 +4601,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4639,7 +4631,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4647,10 +4639,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4659,39 +4649,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4763,12 +4751,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4829,19 +4817,19 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4913,12 +4901,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4943,55 +4931,59 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5016,7 +5008,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5024,8 +5016,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5034,37 +5028,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5089,7 +5085,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5098,7 +5094,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5107,15 +5103,15 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5125,19 +5121,19 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5162,7 +5158,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5170,47 +5166,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5246,9 +5246,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5271,19 +5271,19 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5316,8 +5316,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>1</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5326,37 +5328,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5390,11 +5394,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5417,19 +5421,19 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5501,12 +5505,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5534,17 +5538,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5567,19 +5571,19 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5651,12 +5655,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5681,33 +5685,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5724,12 +5728,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5801,12 +5805,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5831,7 +5835,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5840,24 +5844,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5874,12 +5878,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5951,12 +5955,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5984,17 +5988,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6024,12 +6028,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6101,12 +6105,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6131,33 +6135,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6174,12 +6178,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6251,12 +6255,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6281,33 +6285,33 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6324,12 +6328,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6401,12 +6405,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6431,55 +6435,59 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6551,12 +6559,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6581,7 +6589,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6590,24 +6598,24 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L82" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -6624,12 +6632,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6654,7 +6662,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6662,8 +6670,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6672,37 +6682,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6730,17 +6742,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6770,12 +6782,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6811,9 +6823,9 @@
       <c r="I85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6843,12 +6855,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6873,7 +6885,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6882,24 +6894,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>4</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6916,12 +6928,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6955,11 +6967,11 @@
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6977,7 +6989,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
@@ -6989,12 +7001,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7028,11 +7040,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7062,12 +7074,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7092,7 +7104,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7100,10 +7112,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7112,39 +7122,37 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7178,11 +7186,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7212,12 +7220,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7242,7 +7250,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7250,8 +7258,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7260,37 +7270,39 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7318,17 +7330,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7358,12 +7370,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7388,7 +7400,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7396,47 +7408,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7461,33 +7477,33 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7504,12 +7520,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7534,7 +7550,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7542,8 +7558,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>1</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7552,37 +7570,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7607,7 +7627,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7616,24 +7636,24 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -7650,12 +7670,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7680,7 +7700,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7688,8 +7708,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7698,37 +7720,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7762,11 +7786,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>45</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7796,12 +7820,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7826,7 +7850,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7834,47 +7858,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7902,17 +7930,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7942,12 +7970,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7972,7 +8000,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -7980,8 +8008,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>1</v>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -7990,37 +8020,39 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8045,33 +8077,33 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8088,82 +8120,1846 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,5%</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -742,17 +742,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -898,24 +898,24 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>▼ 40,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,51 +1797,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1952,11 +1948,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1986,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2063,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2102,11 +2098,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2136,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2166,7 +2162,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2174,8 +2170,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2184,37 +2182,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2248,11 +2248,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2323,9 +2323,9 @@
       <c r="I25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2394,11 +2394,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2428,12 +2428,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2467,11 +2467,11 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2501,12 +2501,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2534,17 +2534,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2612,51 +2612,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I29" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2681,7 +2677,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2690,24 +2686,24 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2724,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2754,7 +2750,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2762,51 +2758,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2840,11 +2832,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2874,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2904,7 +2896,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2912,10 +2904,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2924,39 +2914,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2984,17 +2972,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3024,12 +3012,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3101,12 +3089,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3131,7 +3119,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3140,24 +3128,24 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3174,12 +3162,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3251,12 +3239,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3290,7 +3278,7 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3324,12 +3312,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3401,12 +3389,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3440,11 +3428,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3474,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3551,12 +3539,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3590,11 +3578,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3624,12 +3612,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3701,12 +3689,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3742,9 +3730,9 @@
       <c r="I44" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3774,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3851,12 +3839,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3890,11 +3878,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3924,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4001,12 +3989,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4040,11 +4028,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4074,12 +4062,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4151,12 +4139,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4190,11 +4178,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4224,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4301,12 +4289,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4342,9 +4330,9 @@
       <c r="I52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4374,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4451,12 +4439,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4490,11 +4478,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4524,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4601,12 +4589,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4640,11 +4628,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4674,12 +4662,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4751,12 +4739,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4790,7 +4778,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4824,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4901,12 +4889,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4978,12 +4966,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5055,12 +5043,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5128,12 +5116,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5205,12 +5193,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5246,9 +5234,9 @@
       <c r="I64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5278,12 +5266,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5308,7 +5296,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5316,10 +5304,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5328,39 +5314,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5394,11 +5378,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5428,12 +5412,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5458,7 +5442,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5466,51 +5450,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5544,11 +5524,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5578,12 +5558,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5608,7 +5588,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5616,10 +5596,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5628,39 +5606,37 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5694,11 +5670,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5721,19 +5697,19 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5805,12 +5781,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5835,7 +5811,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5846,9 +5822,9 @@
       <c r="I72" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5861,7 +5837,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5871,19 +5847,19 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5955,12 +5931,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5988,17 +5964,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6021,19 +5997,19 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6105,12 +6081,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6135,7 +6111,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6144,24 +6120,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6171,19 +6147,19 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6255,12 +6231,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6294,11 +6270,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6321,19 +6297,19 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6405,12 +6381,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6435,7 +6411,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6443,51 +6419,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I80" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6559,12 +6531,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6598,7 +6570,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6625,19 +6597,19 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6709,12 +6681,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6742,9 +6714,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -6775,19 +6747,19 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6812,7 +6784,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6820,8 +6792,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6830,37 +6804,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6885,7 +6861,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6894,7 +6870,7 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
@@ -6903,15 +6879,15 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6921,19 +6897,19 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6958,7 +6934,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -6966,47 +6942,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7067,19 +7047,19 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7104,7 +7084,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7112,8 +7092,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>1</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7122,37 +7104,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7188,9 +7172,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7213,19 +7197,19 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7297,12 +7281,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7330,17 +7314,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7363,19 +7347,19 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7447,12 +7431,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7477,7 +7461,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7486,24 +7470,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7513,19 +7497,19 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7597,12 +7581,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7636,11 +7620,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7663,19 +7647,19 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7747,12 +7731,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7786,11 +7770,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7813,19 +7797,19 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7897,12 +7881,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7930,17 +7914,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7963,19 +7947,19 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8047,12 +8031,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8077,55 +8061,59 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>9</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8197,12 +8185,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8227,33 +8215,33 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
@@ -8263,19 +8251,19 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8347,12 +8335,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8377,7 +8365,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8386,24 +8374,24 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L106" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -8413,19 +8401,19 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8450,7 +8438,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8458,8 +8446,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8468,37 +8458,39 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8532,11 +8524,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8559,19 +8551,19 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8596,7 +8588,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8604,47 +8596,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8678,11 +8674,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>1</v>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8705,19 +8701,19 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8742,7 +8738,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8750,8 +8746,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>1</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8760,37 +8758,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8818,17 +8818,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -8974,24 +8974,24 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9046,8 +9046,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -9056,37 +9058,39 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9114,17 +9118,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9154,12 +9158,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9184,7 +9188,7 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -9192,47 +9196,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9257,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>2</v>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9300,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9330,7 +9338,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9338,8 +9346,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="n">
-        <v>1</v>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9348,37 +9358,39 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9403,7 +9415,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9412,24 +9424,24 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9446,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9476,7 +9488,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9484,8 +9496,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="n">
-        <v>0</v>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
@@ -9494,37 +9508,39 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9549,7 +9565,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9557,47 +9573,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9622,7 +9642,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9630,47 +9650,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9704,11 +9728,11 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9738,12 +9762,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9768,7 +9792,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9776,8 +9800,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>1</v>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9786,37 +9812,39 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9844,17 +9872,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9884,82 +9912,3184 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>33,3%</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 59,00</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,5%</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8210,7 +8210,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -8810,7 +8810,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -9937,7 +9937,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr">
@@ -11867,7 +11867,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>R$ 69,90</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 54,90</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">

--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -742,17 +742,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -889,33 +889,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,24 +1048,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1500,9 +1500,9 @@
       <c r="I14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2098,11 +2098,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2248,11 +2248,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,14 +2282,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2320,8 +2320,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2330,39 +2332,41 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2394,11 +2398,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2428,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2469,9 +2473,9 @@
       <c r="I27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -2501,14 +2505,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2540,11 +2544,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2574,14 +2578,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2613,11 +2617,11 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2647,14 +2651,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2686,7 +2690,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2720,12 +2724,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2793,12 +2797,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2834,9 +2838,9 @@
       <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2866,12 +2870,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2909,7 +2913,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2939,14 +2943,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2972,17 +2976,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3012,14 +3016,14 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3042,7 +3046,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3050,10 +3054,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3062,41 +3064,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3119,33 +3119,33 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L36" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3162,12 +3162,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3239,14 +3239,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3278,24 +3278,24 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3389,12 +3389,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3580,9 +3580,9 @@
       <c r="I42" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3689,14 +3689,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3728,11 +3728,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3839,14 +3839,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3878,11 +3878,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4030,9 +4030,9 @@
       <c r="I48" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4139,14 +4139,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4178,11 +4178,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4289,14 +4289,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4328,11 +4328,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4439,14 +4439,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4478,11 +4478,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4589,14 +4589,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4628,11 +4628,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4739,14 +4739,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4778,11 +4778,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4889,14 +4889,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4927,10 +4927,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4939,39 +4937,37 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5043,14 +5039,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5073,7 +5069,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5081,8 +5077,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5091,37 +5089,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5193,12 +5193,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5266,14 +5266,14 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5296,7 +5296,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5304,8 +5304,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5314,37 +5316,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5412,12 +5416,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5453,9 +5457,9 @@
       <c r="I67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -5485,12 +5489,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5526,9 +5530,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5558,14 +5562,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5597,11 +5601,11 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5631,14 +5635,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5664,17 +5668,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H70" s="3" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5704,14 +5708,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5734,7 +5738,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5742,10 +5746,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5754,41 +5756,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5811,33 +5811,33 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5931,14 +5931,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5970,24 +5970,24 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6004,12 +6004,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6081,12 +6081,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6122,9 +6122,9 @@
       <c r="I76" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6231,14 +6231,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6270,11 +6270,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6304,12 +6304,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6381,14 +6381,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6420,11 +6420,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6531,12 +6531,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6681,14 +6681,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6720,11 +6720,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6831,14 +6831,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6870,11 +6870,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6981,14 +6981,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7054,12 +7054,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7131,12 +7131,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7172,9 +7172,9 @@
       <c r="I90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7204,12 +7204,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7281,14 +7281,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7320,11 +7320,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7431,12 +7431,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7881,14 +7881,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7920,7 +7920,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7954,12 +7954,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8031,14 +8031,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8061,7 +8061,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8069,10 +8069,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I102" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8081,39 +8079,37 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8185,14 +8181,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8215,7 +8211,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8223,8 +8219,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>0</v>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8233,37 +8231,39 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8376,9 +8376,9 @@
       <c r="I106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8485,14 +8485,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8524,11 +8524,11 @@
         </is>
       </c>
       <c r="I108" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,14 +8635,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8674,11 +8674,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,14 +8785,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8818,17 +8818,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8851,19 +8851,19 @@
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,14 +8935,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8965,33 +8965,33 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J114" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L114" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,14 +9085,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9115,33 +9115,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,14 +9235,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9265,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9428,20 +9428,20 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,14 +9535,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9573,10 +9573,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I122" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9585,39 +9583,37 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9689,14 +9685,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9719,7 +9715,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9727,8 +9723,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9737,37 +9735,39 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9839,14 +9839,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9872,17 +9872,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9912,14 +9912,14 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -9950,8 +9950,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I127" s="2" t="n">
-        <v>0</v>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
@@ -9960,39 +9962,41 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L127" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10015,33 +10019,33 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L128" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -10058,12 +10062,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10099,9 +10103,9 @@
       <c r="I129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -10119,7 +10123,7 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
@@ -10131,14 +10135,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10161,7 +10165,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10170,7 +10174,7 @@
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10179,15 +10183,15 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10204,14 +10208,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10243,11 +10247,11 @@
         </is>
       </c>
       <c r="I131" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10265,7 +10269,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10277,12 +10281,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10350,14 +10354,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10380,7 +10384,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10388,10 +10392,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I133" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10400,41 +10402,39 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10460,17 +10460,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -10500,12 +10500,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10577,14 +10577,14 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10607,33 +10607,33 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10727,14 +10727,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10766,24 +10766,24 @@
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10877,14 +10877,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10916,11 +10916,11 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>▲ 275,0%</t>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -10950,12 +10950,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11027,14 +11027,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11060,17 +11060,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>45</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11100,12 +11100,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11177,14 +11177,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11207,33 +11207,33 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H144" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L144" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11327,12 +11327,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11368,9 +11368,9 @@
       <c r="I146" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11477,14 +11477,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11512,20 +11512,20 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11550,14 +11550,14 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11588,8 +11588,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>0</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11598,39 +11600,41 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11653,7 +11657,7 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -11662,24 +11666,24 @@
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11696,12 +11700,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11737,9 +11741,9 @@
       <c r="I151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -11769,14 +11773,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11808,11 +11812,11 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -11842,14 +11846,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11881,11 +11885,11 @@
         </is>
       </c>
       <c r="I153" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11915,14 +11919,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11954,11 +11958,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▲ 112,5%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11988,14 +11992,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12018,7 +12022,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12026,10 +12030,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I155" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -12038,41 +12040,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12104,11 +12104,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12138,14 +12138,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12176,8 +12176,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12186,39 +12188,41 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12250,11 +12254,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>8</v>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12284,12 +12288,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12325,9 +12329,9 @@
       <c r="I159" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -12345,7 +12349,7 @@
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
@@ -12357,14 +12361,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12390,17 +12394,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12430,14 +12434,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12469,11 +12473,11 @@
         </is>
       </c>
       <c r="I161" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12503,14 +12507,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12533,33 +12537,33 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12576,14 +12580,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12615,7 +12619,7 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
@@ -12649,14 +12653,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12679,7 +12683,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12688,24 +12692,24 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12722,12 +12726,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12763,9 +12767,9 @@
       <c r="I165" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J165" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12795,14 +12799,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12834,11 +12838,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12868,14 +12872,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12907,11 +12911,11 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12941,14 +12945,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12980,11 +12984,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13014,82 +13018,228 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 54,90</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -892,17 +892,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1039,33 +1039,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1198,24 +1198,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1348,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1650,9 +1650,9 @@
       <c r="I16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,14 +1759,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1798,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2098,11 +2098,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2248,11 +2248,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2398,11 +2398,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2432,14 +2432,14 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2470,8 +2470,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2480,39 +2482,41 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2544,11 +2548,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▲ 75,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2578,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2619,9 +2623,9 @@
       <c r="I29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -2651,14 +2655,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2690,11 +2694,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2724,14 +2728,14 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2763,11 +2767,11 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2797,14 +2801,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2836,7 +2840,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2870,12 +2874,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2943,12 +2947,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2984,9 +2988,9 @@
       <c r="I34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3016,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3059,7 +3063,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3089,14 +3093,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3122,17 +3126,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3162,14 +3166,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3192,7 +3196,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3200,10 +3204,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3212,41 +3214,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3269,33 +3269,33 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L38" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3389,14 +3389,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3428,24 +3428,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3730,9 +3730,9 @@
       <c r="I44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3839,14 +3839,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3878,11 +3878,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3989,14 +3989,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4028,11 +4028,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4180,9 +4180,9 @@
       <c r="I50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4289,14 +4289,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4328,11 +4328,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4439,14 +4439,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4478,11 +4478,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4589,14 +4589,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4628,11 +4628,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4739,14 +4739,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4778,11 +4778,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4889,14 +4889,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4928,11 +4928,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5039,14 +5039,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5077,10 +5077,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5089,39 +5087,37 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5193,14 +5189,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5223,7 +5219,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5231,8 +5227,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5241,37 +5239,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5416,14 +5416,14 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5446,7 +5446,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5454,8 +5454,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5464,37 +5466,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5562,12 +5566,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5603,9 +5607,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5635,12 +5639,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5676,9 +5680,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5708,14 +5712,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5747,11 +5751,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5781,14 +5785,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5814,17 +5818,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5854,14 +5858,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5884,7 +5888,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5892,10 +5896,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5904,41 +5906,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5961,33 +5961,33 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -6004,12 +6004,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6081,14 +6081,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6120,24 +6120,24 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6231,12 +6231,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6272,9 +6272,9 @@
       <c r="I78" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6304,12 +6304,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6381,14 +6381,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6420,11 +6420,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>▲ 500,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6531,14 +6531,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6570,11 +6570,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6831,14 +6831,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6870,11 +6870,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6981,14 +6981,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7020,11 +7020,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7131,14 +7131,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7170,7 +7170,7 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
@@ -7204,12 +7204,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7281,12 +7281,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7322,9 +7322,9 @@
       <c r="I92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7431,14 +7431,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7470,11 +7470,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8031,14 +8031,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8104,12 +8104,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8181,14 +8181,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8219,10 +8219,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8231,39 +8229,37 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8335,14 +8331,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8365,7 +8361,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8373,8 +8369,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n">
-        <v>0</v>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8383,37 +8381,39 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8526,9 +8526,9 @@
       <c r="I108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J108" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,14 +8635,14 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8674,11 +8674,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,14 +8785,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8824,11 +8824,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,14 +8935,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8968,17 +8968,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -9001,19 +9001,19 @@
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,14 +9085,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9115,33 +9115,33 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L116" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -9158,12 +9158,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,14 +9235,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9265,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9415,33 +9415,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,14 +9535,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9578,20 +9578,20 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9685,14 +9685,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9723,10 +9723,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I124" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9735,39 +9733,37 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9839,14 +9835,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9869,7 +9865,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9877,8 +9873,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
-        <v>0</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9887,37 +9885,39 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9989,14 +9989,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10022,17 +10022,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J128" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -10062,14 +10062,14 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -10100,8 +10100,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="2" t="n">
-        <v>0</v>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
@@ -10110,39 +10112,41 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L129" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10165,33 +10169,33 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L130" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -10208,12 +10212,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10249,9 +10253,9 @@
       <c r="I131" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J131" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -10269,7 +10273,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
@@ -10281,14 +10285,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10311,7 +10315,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10320,7 +10324,7 @@
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10329,15 +10333,15 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10354,14 +10358,14 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10393,11 +10397,11 @@
         </is>
       </c>
       <c r="I133" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10415,7 +10419,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10427,12 +10431,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10500,14 +10504,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10530,7 +10534,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10538,10 +10542,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
@@ -10550,41 +10552,39 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10610,17 +10610,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10727,14 +10727,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10757,33 +10757,33 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L138" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10877,14 +10877,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -10916,24 +10916,24 @@
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10950,12 +10950,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11027,14 +11027,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11066,11 +11066,11 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▲ 275,0%</t>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -11100,12 +11100,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11177,14 +11177,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11210,17 +11210,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H144" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>45</v>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11327,14 +11327,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11357,33 +11357,33 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H146" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L146" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11518,9 +11518,9 @@
       <c r="I148" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11627,14 +11627,14 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11662,20 +11662,20 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>9</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11700,14 +11700,14 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -11738,8 +11738,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I151" s="2" t="n">
-        <v>0</v>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11748,39 +11750,41 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L151" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11803,7 +11807,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11812,24 +11816,24 @@
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11846,12 +11850,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11887,9 +11891,9 @@
       <c r="I153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -11919,14 +11923,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11958,11 +11962,11 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>▼ 41,2%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -11992,14 +11996,14 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12031,11 +12035,11 @@
         </is>
       </c>
       <c r="I155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12065,14 +12069,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12104,11 +12108,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>▲ 112,5%</t>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12138,14 +12142,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12168,7 +12172,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12176,10 +12180,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12188,41 +12190,39 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12254,11 +12254,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12288,14 +12288,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12326,8 +12326,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>0</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12336,39 +12338,41 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12400,11 +12404,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>8</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12434,12 +12438,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12475,9 +12479,9 @@
       <c r="I161" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -12495,7 +12499,7 @@
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
@@ -12507,14 +12511,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12540,17 +12544,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H162" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▲ 18,2%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12580,14 +12584,14 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12619,11 +12623,11 @@
         </is>
       </c>
       <c r="I163" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12653,14 +12657,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12683,33 +12687,33 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▲ 120,0%</t>
+        <v>13</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -12726,14 +12730,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12765,7 +12769,7 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
@@ -12799,14 +12803,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12829,7 +12833,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12838,24 +12842,24 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12872,12 +12876,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12913,9 +12917,9 @@
       <c r="I167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -12945,14 +12949,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12984,11 +12988,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J168" s="4" t="inlineStr">
-        <is>
-          <t>▼ 25,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13018,14 +13022,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -13057,11 +13061,11 @@
         </is>
       </c>
       <c r="I169" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13091,14 +13095,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -13130,11 +13134,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13164,82 +13168,228 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 54,90</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +859,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1009,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1042,17 +1042,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1159,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1189,33 +1189,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1309,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1348,24 +1348,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 40,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1459,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,14 +1609,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1800,9 +1800,9 @@
       <c r="I18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,14 +1909,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,14 +2059,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2098,11 +2098,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>4</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,14 +2209,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2248,11 +2248,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,14 +2359,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2398,11 +2398,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,14 +2509,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2548,11 +2548,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>▼ 42,9%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2582,14 +2582,14 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2620,8 +2620,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
@@ -2630,39 +2632,41 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2694,11 +2698,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2728,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2769,9 +2773,9 @@
       <c r="I31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2801,14 +2805,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2840,11 +2844,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>7</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2874,14 +2878,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2913,11 +2917,11 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2947,14 +2951,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -2986,7 +2990,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3020,12 +3024,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3093,12 +3097,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3134,9 +3138,9 @@
       <c r="I36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3166,12 +3170,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3209,7 +3213,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3239,14 +3243,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3272,17 +3276,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3312,14 +3316,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3342,7 +3346,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3350,10 +3354,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3362,41 +3364,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3419,33 +3419,33 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>▼ 33,3%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3462,12 +3462,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3539,14 +3539,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3578,24 +3578,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3612,12 +3612,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3880,9 +3880,9 @@
       <c r="I46" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3912,12 +3912,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3989,14 +3989,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4028,11 +4028,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4139,14 +4139,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4178,11 +4178,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4330,9 +4330,9 @@
       <c r="I52" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4439,14 +4439,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4478,11 +4478,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4589,14 +4589,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4628,11 +4628,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4739,14 +4739,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4778,11 +4778,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4889,14 +4889,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -4928,11 +4928,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 57,1%</t>
+        <v>4</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5039,14 +5039,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5078,11 +5078,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5189,14 +5189,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5227,10 +5227,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5239,39 +5237,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5343,14 +5339,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5373,7 +5369,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5381,8 +5377,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5391,37 +5389,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5566,14 +5566,14 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5604,8 +5604,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5614,37 +5616,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5712,12 +5716,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5753,9 +5757,9 @@
       <c r="I71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5785,12 +5789,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5826,9 +5830,9 @@
       <c r="I72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5858,14 +5862,14 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5897,11 +5901,11 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -5931,14 +5935,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -5964,17 +5968,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H74" s="3" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6004,14 +6008,14 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6034,7 +6038,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6042,10 +6046,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I75" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6054,41 +6056,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6111,33 +6111,33 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>▼ 60,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6231,14 +6231,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6270,24 +6270,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6304,12 +6304,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6422,9 +6422,9 @@
       <c r="I80" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6531,14 +6531,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6570,11 +6570,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6681,14 +6681,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -6720,11 +6720,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6981,14 +6981,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7020,11 +7020,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7131,14 +7131,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7170,11 +7170,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7204,12 +7204,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7281,14 +7281,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7320,7 +7320,7 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7354,12 +7354,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7431,12 +7431,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7472,9 +7472,9 @@
       <c r="I94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7581,14 +7581,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -7620,11 +7620,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8181,14 +8181,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8254,12 +8254,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8331,14 +8331,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8369,10 +8369,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8381,39 +8379,37 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8485,14 +8481,14 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8515,7 +8511,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8523,8 +8519,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n">
-        <v>0</v>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8533,37 +8531,39 @@
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,12 +8635,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8676,9 +8676,9 @@
       <c r="I110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,14 +8785,14 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8824,11 +8824,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,14 +8935,14 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -8974,11 +8974,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,14 +9085,14 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
-        </is>
-      </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9118,17 +9118,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -9151,19 +9151,19 @@
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,14 +9235,14 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
-        </is>
-      </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9265,33 +9265,33 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L118" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,14 +9385,14 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
-        </is>
-      </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9415,33 +9415,33 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,14 +9535,14 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
-        </is>
-      </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9565,33 +9565,33 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L122" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
@@ -9608,12 +9608,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9685,14 +9685,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9728,20 +9728,20 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9835,14 +9835,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -9865,7 +9865,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9873,10 +9873,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I126" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9885,39 +9883,37 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9989,14 +9985,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10019,7 +10015,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10027,8 +10023,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="n">
-        <v>0</v>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -10037,37 +10035,39 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10139,14 +10139,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10172,17 +10172,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10212,14 +10212,14 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
-        </is>
-      </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -10250,8 +10250,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I131" s="2" t="n">
-        <v>0</v>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
@@ -10260,39 +10262,41 @@
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L131" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10315,33 +10319,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10358,12 +10362,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10399,9 +10403,9 @@
       <c r="I133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -10419,7 +10423,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
@@ -10431,14 +10435,14 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10461,7 +10465,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10470,7 +10474,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10479,15 +10483,15 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10504,14 +10508,14 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
-        </is>
-      </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10543,11 +10547,11 @@
         </is>
       </c>
       <c r="I135" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -10565,7 +10569,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
@@ -10577,12 +10581,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10650,14 +10654,14 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
-        </is>
-      </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10680,7 +10684,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10688,10 +10692,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I137" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10700,41 +10702,39 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10760,17 +10760,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -10800,12 +10800,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10877,14 +10877,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -10907,33 +10907,33 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>▼ 75,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L140" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
@@ -10950,12 +10950,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11027,14 +11027,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -11066,24 +11066,24 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>▼ 73,3%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11100,12 +11100,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11177,14 +11177,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11216,11 +11216,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>12</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11327,14 +11327,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11360,17 +11360,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="J146" s="4" t="inlineStr">
         <is>
-          <t>▲ 33,3%</t>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11477,14 +11477,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11507,33 +11507,33 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
-        </is>
-      </c>
-      <c r="H148" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>12</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L148" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11668,9 +11668,9 @@
       <c r="I150" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>▼ 10,0%</t>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11777,14 +11777,14 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11812,20 +11812,20 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11850,14 +11850,14 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
-        </is>
-      </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -11888,8 +11888,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="n">
-        <v>0</v>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -11898,39 +11900,41 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -11953,7 +11957,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11962,24 +11966,24 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>10</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -11996,12 +12000,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12037,9 +12041,9 @@
       <c r="I155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -12069,14 +12073,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12108,11 +12112,11 @@
         </is>
       </c>
       <c r="I156" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>12</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12142,14 +12146,14 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
-        </is>
-      </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12181,11 +12185,11 @@
         </is>
       </c>
       <c r="I157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -12215,14 +12219,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12254,11 +12258,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>10</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12288,14 +12292,14 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12318,7 +12322,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12326,10 +12330,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I159" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12338,41 +12340,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12404,11 +12404,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 20,0%</t>
+        <v>17</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12438,14 +12438,14 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
-        </is>
-      </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -12476,8 +12476,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I161" s="2" t="n">
-        <v>0</v>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
@@ -12486,39 +12488,41 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L161" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N161" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12550,11 +12554,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 23,1%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12584,12 +12588,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12625,9 +12629,9 @@
       <c r="I163" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -12645,7 +12649,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12657,14 +12661,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12690,17 +12694,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12730,14 +12734,14 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12769,11 +12773,11 @@
         </is>
       </c>
       <c r="I165" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -12803,14 +12807,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12833,33 +12837,33 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J166" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L166" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -12876,14 +12880,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12915,7 +12919,7 @@
         </is>
       </c>
       <c r="I167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -12949,14 +12953,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -12979,7 +12983,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -12988,24 +12992,24 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>11</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13022,12 +13026,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13063,9 +13067,9 @@
       <c r="I169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -13095,14 +13099,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -13134,11 +13138,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13168,14 +13172,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -13207,11 +13211,11 @@
         </is>
       </c>
       <c r="I171" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13241,14 +13245,14 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>UTD-031</t>
@@ -13280,11 +13284,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13314,82 +13318,228 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 54,90</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
+++ b/saida_skus/SKU_UTD-031-CENTRO-MESA-FOLHA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -598,24 +598,24 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+        <v>6</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 25,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1192,17 +1192,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1357,15 +1357,15 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 40,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 150,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1682,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1792,17 +1792,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1948,24 +1948,24 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2098,11 +2098,11 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▲ 300,0%</t>
+          <t>▲ 40,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2248,11 +2248,11 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>5</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2398,11 +2398,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2432,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2700,9 +2700,9 @@
       <c r="I30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 42,9%</t>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2770,8 +2770,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2780,37 +2782,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2844,11 +2848,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 75,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2878,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2908,7 +2912,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2916,47 +2920,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2990,11 +2998,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3024,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3054,7 +3062,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3062,47 +3070,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>1</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3136,11 +3148,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3170,12 +3182,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3200,7 +3212,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3208,47 +3220,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>1</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3282,11 +3298,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 42,9%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3316,12 +3332,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3355,7 +3371,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3389,12 +3405,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3422,17 +3438,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 75,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3462,12 +3478,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3492,7 +3508,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3500,51 +3516,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3569,7 +3581,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3578,24 +3590,24 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>4</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L42" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3612,12 +3624,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3642,7 +3654,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3650,51 +3662,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3728,11 +3736,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3762,12 +3770,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3792,7 +3800,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3800,51 +3808,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3878,11 +3882,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3912,12 +3916,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3942,7 +3946,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3950,10 +3954,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I47" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -3962,39 +3964,37 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4022,17 +4022,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4062,12 +4062,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4178,24 +4178,24 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4362,12 +4362,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4480,9 +4480,9 @@
       <c r="I54" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 40,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4589,12 +4589,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4628,11 +4628,11 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>▲ 150,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4739,12 +4739,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4778,11 +4778,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4928,11 +4928,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>▼ 57,1%</t>
+          <t>▼ 40,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5228,11 +5228,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 150,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5262,12 +5262,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5377,51 +5377,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5493,12 +5489,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5532,11 +5528,11 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>4</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5566,12 +5562,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5643,12 +5639,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5682,11 +5678,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 57,1%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5716,12 +5712,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5746,7 +5742,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5754,8 +5750,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5764,37 +5762,39 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5862,12 +5862,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5900,47 +5900,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5965,7 +5969,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -5973,47 +5977,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6038,7 +6046,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6046,8 +6054,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>1</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6056,37 +6066,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6114,17 +6126,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6154,12 +6166,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6231,12 +6243,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6261,7 +6273,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 70,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6270,24 +6282,24 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 60,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -6304,12 +6316,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6334,7 +6346,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6342,10 +6354,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6354,39 +6364,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6420,11 +6428,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6454,12 +6462,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6484,7 +6492,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6492,51 +6500,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6570,11 +6574,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6604,12 +6608,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6634,7 +6638,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6642,10 +6646,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6654,39 +6656,37 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6714,17 +6714,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 500,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6870,24 +6870,24 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 60,0%</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -6904,12 +6904,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6981,12 +6981,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7020,11 +7020,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7054,12 +7054,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7131,12 +7131,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7170,11 +7170,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>▼ 100,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7204,12 +7204,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7281,12 +7281,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7320,11 +7320,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 500,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7431,12 +7431,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7470,11 +7470,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7620,11 +7620,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7770,11 +7770,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7920,11 +7920,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8070,11 +8070,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8181,12 +8181,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8220,11 +8220,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8331,12 +8331,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8370,11 +8370,11 @@
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -8519,51 +8519,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I108" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8635,12 +8631,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8674,11 +8670,11 @@
         </is>
       </c>
       <c r="I110" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -8708,12 +8704,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8785,12 +8781,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8824,11 +8820,11 @@
         </is>
       </c>
       <c r="I112" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -8858,12 +8854,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8935,12 +8931,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -8974,11 +8970,11 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -9008,12 +9004,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9085,12 +9081,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9115,7 +9111,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9123,8 +9119,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>1</v>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9133,37 +9131,39 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Ruim</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9268,17 +9268,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -9301,19 +9301,19 @@
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9385,12 +9385,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9424,24 +9424,24 @@
         </is>
       </c>
       <c r="I120" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
@@ -9451,19 +9451,19 @@
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9535,12 +9535,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9568,17 +9568,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -9601,19 +9601,19 @@
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9724,24 +9724,24 @@
         </is>
       </c>
       <c r="I124" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
@@ -9751,19 +9751,19 @@
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9868,17 +9868,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -9985,12 +9985,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10023,51 +10023,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10139,12 +10135,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10172,17 +10168,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>1</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -10212,12 +10208,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10289,12 +10285,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10319,33 +10315,33 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 57,00</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L132" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -10362,12 +10358,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10392,7 +10388,7 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -10400,8 +10396,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I133" s="2" t="n">
-        <v>0</v>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10410,37 +10408,39 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L133" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>R$ 57,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
         </is>
       </c>
       <c r="I134" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
@@ -10483,15 +10483,15 @@
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L134" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -10546,47 +10546,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I135" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L135" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10611,7 +10615,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -10619,8 +10623,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I136" s="2" t="n">
-        <v>0</v>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
@@ -10629,37 +10635,39 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L136" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10684,7 +10692,7 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -10692,8 +10700,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I137" s="2" t="n">
-        <v>1</v>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
@@ -10702,37 +10712,39 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L137" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10800,12 +10812,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10877,12 +10889,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -10950,12 +10962,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -10980,7 +10992,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -10988,10 +11000,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11000,39 +11010,37 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11066,16 +11074,16 @@
         </is>
       </c>
       <c r="I142" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+        <v>4</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="L142" s="2" t="n">
@@ -11083,7 +11091,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
@@ -11100,12 +11108,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11130,7 +11138,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11138,51 +11146,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11216,11 +11220,11 @@
         </is>
       </c>
       <c r="I144" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>▼ 73,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -11250,12 +11254,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11280,7 +11284,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11288,10 +11292,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11300,39 +11302,37 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11366,11 +11366,11 @@
         </is>
       </c>
       <c r="I146" s="2" t="n">
-        <v>45</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>▲ 275,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11516,11 +11516,11 @@
         </is>
       </c>
       <c r="I148" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>▲ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -11550,12 +11550,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11657,25 +11657,25 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 57,00</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L150" s="2" t="n">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="N150" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11807,33 +11807,33 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>▼ 10,0%</t>
+          <t>▼ 73,3%</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L152" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
@@ -11850,12 +11850,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11927,12 +11927,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 59,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -11966,24 +11966,24 @@
         </is>
       </c>
       <c r="I154" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>45</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>▲ 275,0%</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L154" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
@@ -12000,12 +12000,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12038,8 +12038,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="n">
-        <v>0</v>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
@@ -12048,37 +12050,39 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12106,9 +12110,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
@@ -12116,7 +12120,7 @@
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 33,3%</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12146,12 +12150,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12176,7 +12180,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12184,47 +12188,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12249,33 +12257,33 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 41,2%</t>
+        <v>9</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
@@ -12292,12 +12300,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12322,7 +12330,7 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -12330,8 +12338,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I159" s="2" t="n">
-        <v>1</v>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
@@ -12340,37 +12350,39 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L159" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N159" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12395,33 +12407,33 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>▲ 112,5%</t>
+        <v>9</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 10,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="L160" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -12438,12 +12450,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12515,12 +12527,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12545,7 +12557,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 59,00</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12554,24 +12566,24 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>▼ 20,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="L162" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -12588,12 +12600,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12649,7 +12661,7 @@
       </c>
       <c r="N163" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O163" s="2" t="inlineStr">
@@ -12661,12 +12673,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12700,11 +12712,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 23,1%</t>
+        <v>12</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12734,12 +12746,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12807,12 +12819,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12840,17 +12852,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>▲ 18,2%</t>
+        <v>10</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 41,2%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -12880,12 +12892,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -12953,12 +12965,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -12983,7 +12995,7 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>R$ 55,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -12992,24 +13004,24 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>▲ 120,0%</t>
+          <t>▲ 112,5%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -13026,12 +13038,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13056,7 +13068,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -13064,8 +13076,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="n">
-        <v>0</v>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -13074,37 +13088,39 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13138,11 +13154,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 20,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13172,12 +13188,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13213,9 +13229,9 @@
       <c r="I171" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -13233,7 +13249,7 @@
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
@@ -13245,12 +13261,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13284,11 +13300,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>▼ 25,0%</t>
+          <t>▼ 23,1%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13318,12 +13334,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13357,11 +13373,11 @@
         </is>
       </c>
       <c r="I173" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J173" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -13391,12 +13407,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13424,17 +13440,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>13</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>▲ 18,2%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13464,82 +13480,666 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 55,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>▲ 120,0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J178" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 25,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4533720905</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-031</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Centro mesa folha</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>6464958514</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-031</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Centro mesa folha</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4533720905</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 54,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 54,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>